--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.286731148227483</v>
+        <v>0.6965938115869661</v>
       </c>
       <c r="D2" t="n">
-        <v>3.977387981544239</v>
+        <v>0.6463255470009388</v>
       </c>
       <c r="E2" t="n">
-        <v>29.27776686910684</v>
+        <v>4.757637116229862</v>
       </c>
       <c r="F2" t="n">
-        <v>29.03887639541919</v>
+        <v>4.718817414255618</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.64911474938026</v>
+        <v>3.842981146774293</v>
       </c>
       <c r="D3" t="n">
-        <v>24.39004863031627</v>
+        <v>3.963382902426393</v>
       </c>
       <c r="E3" t="n">
-        <v>29.27776686910684</v>
+        <v>4.757637116229862</v>
       </c>
       <c r="F3" t="n">
-        <v>29.03887639541919</v>
+        <v>4.718817414255618</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>73.76899253580477</v>
+        <v>11.98746128706828</v>
       </c>
       <c r="D4" t="n">
-        <v>73.19342940771847</v>
+        <v>11.89393227875425</v>
       </c>
       <c r="E4" t="n">
-        <v>29.27776686910684</v>
+        <v>4.757637116229862</v>
       </c>
       <c r="F4" t="n">
-        <v>29.03887639541919</v>
+        <v>4.718817414255618</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
